--- a/UTCUTS/A1_Outputs/reference_works/A-O_Fleet_REF.xlsx
+++ b/UTCUTS/A1_Outputs/reference_works/A-O_Fleet_REF.xlsx
@@ -625,7 +625,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD11353F-2796-4AB5-8F47-B01E81E3E2FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0940FC5-6438-41E6-8D01-6A8B4737758C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
